--- a/artfynd/A 66118-2020 artfynd.xlsx
+++ b/artfynd/A 66118-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66118-2020 artfynd.xlsx
+++ b/artfynd/A 66118-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72413784</v>
+        <v>72413824</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>77506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438915.8072300788</v>
+        <v>438940.7089671008</v>
       </c>
       <c r="R2" t="n">
-        <v>7166939.394283689</v>
+        <v>7166767.649757651</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72413824</v>
+        <v>72427238</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>storhögen, Jmt</t>
+          <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438940.7089671008</v>
+        <v>438788.1599838944</v>
       </c>
       <c r="R3" t="n">
-        <v>7166767.649757651</v>
+        <v>7167299.874322301</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,29 +884,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72427238</v>
+        <v>72427229</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
+        <v>77506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438788.1599838944</v>
+        <v>438816.0301957426</v>
       </c>
       <c r="R4" t="n">
-        <v>7167299.874322301</v>
+        <v>7167062.858398716</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72427229</v>
+        <v>72427244</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
+        <v>77668</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438816.0301957426</v>
+        <v>438900.1089217712</v>
       </c>
       <c r="R5" t="n">
-        <v>7167062.858398716</v>
+        <v>7167247.837880625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72427244</v>
+        <v>72427251</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
+        <v>77506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438900.1089217712</v>
+        <v>438997.8436271814</v>
       </c>
       <c r="R6" t="n">
-        <v>7167247.837880625</v>
+        <v>7167087.089453592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72427251</v>
+        <v>72427254</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438997.8436271814</v>
+        <v>438902.8563449386</v>
       </c>
       <c r="R7" t="n">
-        <v>7167087.089453592</v>
+        <v>7167170.968182585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72427254</v>
+        <v>72427246</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
+        <v>73686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438902.8563449386</v>
+        <v>438773.1407338728</v>
       </c>
       <c r="R8" t="n">
-        <v>7167170.968182585</v>
+        <v>7167322.062578341</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72427246</v>
+        <v>72427250</v>
       </c>
       <c r="B9" t="n">
-        <v>73686</v>
+        <v>77506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438773.1407338728</v>
+        <v>438873.9904148155</v>
       </c>
       <c r="R9" t="n">
-        <v>7167322.062578341</v>
+        <v>7166826.076082955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72427250</v>
+        <v>72427245</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
+        <v>78603</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,25 +1614,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438873.9904148155</v>
+        <v>438773.1407338728</v>
       </c>
       <c r="R10" t="n">
-        <v>7166826.076082955</v>
+        <v>7167322.062578341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>72427245</v>
+        <v>72427230</v>
       </c>
       <c r="B11" t="n">
-        <v>78603</v>
+        <v>89410</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,25 +1730,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438773.1407338728</v>
+        <v>438816.0301957426</v>
       </c>
       <c r="R11" t="n">
-        <v>7167322.062578341</v>
+        <v>7167062.858398716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>72427230</v>
+        <v>72427255</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
+        <v>73686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438816.0301957426</v>
+        <v>438902.8563449386</v>
       </c>
       <c r="R12" t="n">
-        <v>7167062.858398716</v>
+        <v>7167170.968182585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>72427255</v>
+        <v>72427247</v>
       </c>
       <c r="B13" t="n">
-        <v>73686</v>
+        <v>78570</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,21 +1966,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438902.8563449386</v>
+        <v>438773.1407338728</v>
       </c>
       <c r="R13" t="n">
-        <v>7167170.968182585</v>
+        <v>7167322.062578341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2067,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72427247</v>
+        <v>72427228</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,21 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438773.1407338728</v>
+        <v>438816.0301957426</v>
       </c>
       <c r="R14" t="n">
-        <v>7167322.062578341</v>
+        <v>7167062.858398716</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72427228</v>
+        <v>72427236</v>
       </c>
       <c r="B15" t="n">
-        <v>73698</v>
+        <v>78570</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,21 +2198,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438816.0301957426</v>
+        <v>438969.0578247713</v>
       </c>
       <c r="R15" t="n">
-        <v>7167062.858398716</v>
+        <v>7167001.838156499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2299,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>72427236</v>
+        <v>72427249</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
+        <v>89410</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,21 +2314,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438969.0578247713</v>
+        <v>438904.9196643754</v>
       </c>
       <c r="R16" t="n">
-        <v>7167001.838156499</v>
+        <v>7167252.032173482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>72427249</v>
+        <v>72427248</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
+        <v>76863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,25 +2426,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438904.9196643754</v>
+        <v>438977.9266300052</v>
       </c>
       <c r="R17" t="n">
-        <v>7167252.032173482</v>
+        <v>7167036.850491153</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72427248</v>
+        <v>72427237</v>
       </c>
       <c r="B18" t="n">
-        <v>76863</v>
+        <v>78570</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,25 +2542,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438977.9266300052</v>
+        <v>438877.9142534828</v>
       </c>
       <c r="R18" t="n">
-        <v>7167036.850491153</v>
+        <v>7167255.151270687</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,14 +2646,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72427237</v>
+        <v>72427231</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2663,21 +2662,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2687,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438877.9142534828</v>
+        <v>438816.0301957426</v>
       </c>
       <c r="R19" t="n">
-        <v>7167255.151270687</v>
+        <v>7167062.858398716</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,6 +2734,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2756,127 +2760,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>72427231</v>
-      </c>
-      <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>438816.0301957426</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7167062.858398716</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2018-07-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2018-07-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
